--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PYTHON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A18787-3CF1-470C-94D9-FFCFBD1F13AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F344ADA5-C6E0-4EB0-BA5A-B9F5A8B1A360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19590" yWindow="3510" windowWidth="19710" windowHeight="11760" xr2:uid="{DCFC37B5-4297-477E-8BA8-2320095023A1}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294910033" uniqueCount="72">
   <si>
     <t>Precio Compra</t>
   </si>
@@ -235,6 +235,27 @@
   </si>
   <si>
     <t>74190446.jpg</t>
+  </si>
+  <si>
+    <t>68020142</t>
+  </si>
+  <si>
+    <t>CARTUCHO MS-BOSTIK ANTRACITA 290 ML</t>
+  </si>
+  <si>
+    <t>68020143</t>
+  </si>
+  <si>
+    <t>CARTUCHO MS-BOSTIK TEJA 290 ML</t>
+  </si>
+  <si>
+    <t>68020142.jpg</t>
+  </si>
+  <si>
+    <t>68020143.jpg</t>
+  </si>
+  <si>
+    <t>cant of</t>
   </si>
 </sst>
 </file>
@@ -250,15 +271,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -266,12 +293,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,13 +677,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED20D23-1B19-4647-8C7A-B348F7A492AC}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -643,8 +715,11 @@
       <c r="J1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -673,7 +748,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -702,7 +777,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -731,7 +806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -760,7 +835,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -789,7 +864,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -820,8 +895,11 @@
       <c r="J7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -852,8 +930,11 @@
       <c r="J8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -884,8 +965,11 @@
       <c r="J9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -916,8 +1000,11 @@
       <c r="J10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -946,7 +1033,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -975,7 +1062,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1004,7 +1091,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1033,7 +1120,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1062,7 +1149,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1091,7 +1178,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1120,7 +1207,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1149,7 +1236,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1181,7 +1268,152 @@
         <v>64</v>
       </c>
     </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8.25</v>
+      </c>
+      <c r="G20" s="2">
+        <v>40</v>
+      </c>
+      <c r="H20" s="2">
+        <v>4.95</v>
+      </c>
+      <c r="I20" s="5">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F21" s="4">
+        <v>8.25</v>
+      </c>
+      <c r="G21" s="4">
+        <v>40</v>
+      </c>
+      <c r="H21" s="4">
+        <v>4.95</v>
+      </c>
+      <c r="I21" s="6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J21" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8.25</v>
+      </c>
+      <c r="G22" s="2">
+        <v>40</v>
+      </c>
+      <c r="H22" s="2">
+        <v>4.95</v>
+      </c>
+      <c r="I22" s="5">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J22" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F23" s="4">
+        <v>8.25</v>
+      </c>
+      <c r="G23" s="4">
+        <v>40</v>
+      </c>
+      <c r="H23" s="4">
+        <v>4.95</v>
+      </c>
+      <c r="I23" s="6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J23" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="I20:I23 K20 K22">
+    <cfRule type="expression" priority="1">
+      <formula>AND(ISNUMBER(I24), I24&gt;0, TRIM(I24)&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1189,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F341BEB-67D3-4B35-989A-F8410DBADF8C}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1212,7 +1444,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="str">
-        <f t="shared" ref="C2:C18" si="0">CONCATENATE(A2,B2)</f>
+        <f t="shared" ref="C2:C20" si="0">CONCATENATE(A2,B2)</f>
         <v>74191426.jpg</v>
       </c>
     </row>
@@ -1406,6 +1638,30 @@
       <c r="C18" t="str">
         <f t="shared" si="0"/>
         <v>74190446.jpg</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>68020142.jpg</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>68020143.jpg</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\PYTHON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F344ADA5-C6E0-4EB0-BA5A-B9F5A8B1A360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7625DE-BD6F-4C66-9155-1DC3471A2DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19590" yWindow="3510" windowWidth="19710" windowHeight="11760" xr2:uid="{DCFC37B5-4297-477E-8BA8-2320095023A1}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$K$17</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294910033" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294910015" uniqueCount="60">
   <si>
     <t>Precio Compra</t>
   </si>
@@ -105,15 +108,9 @@
     <t>74380002</t>
   </si>
   <si>
-    <t>SET TALADRO ATORNILLADOR + MALETIN 78PZ 602245710</t>
-  </si>
-  <si>
     <t>52002875</t>
   </si>
   <si>
-    <t>SET TALADRO ATORNILLADOR +ACCS SB 18 L 614053710</t>
-  </si>
-  <si>
     <t>74250088</t>
   </si>
   <si>
@@ -135,15 +132,9 @@
     <t>74170881</t>
   </si>
   <si>
-    <t>TALADRO 750W TM 750AK 1.5449 KLAVO</t>
-  </si>
-  <si>
     <t>52002886</t>
   </si>
   <si>
-    <t>TALADRO 850W BE 850-2 600573810 METABO</t>
-  </si>
-  <si>
     <t>74170880</t>
   </si>
   <si>
@@ -159,9 +150,6 @@
     <t>52002112</t>
   </si>
   <si>
-    <t>TALADRO ATORNILLADOR SB18 LT BL 602316500 2 BAT 4AH ASC55</t>
-  </si>
-  <si>
     <t>74460003</t>
   </si>
   <si>
@@ -177,9 +165,6 @@
     <t>52003151</t>
   </si>
   <si>
-    <t>TALADRO PERCUTOR 810W EMDL0811 EMTOP</t>
-  </si>
-  <si>
     <t>74190448</t>
   </si>
   <si>
@@ -192,12 +177,6 @@
     <t>TALADRO PERCUTOR SBE 650+SET 600671870</t>
   </si>
   <si>
-    <t>74380002.jpg</t>
-  </si>
-  <si>
-    <t>52002875.jpg</t>
-  </si>
-  <si>
     <t>74250088.jpg</t>
   </si>
   <si>
@@ -207,28 +186,16 @@
     <t>74200072.jpg</t>
   </si>
   <si>
-    <t>74170881.jpg</t>
-  </si>
-  <si>
-    <t>52002886.jpg</t>
-  </si>
-  <si>
     <t>74170880.jpg</t>
   </si>
   <si>
     <t>74460004.jpg</t>
   </si>
   <si>
-    <t>52002112.jpg</t>
-  </si>
-  <si>
     <t>74460003.jpg</t>
   </si>
   <si>
     <t>74230026.jpg</t>
-  </si>
-  <si>
-    <t>52003151.jpg</t>
   </si>
   <si>
     <t>74190448.jpg</t>
@@ -334,15 +301,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED20D23-1B19-4647-8C7A-B348F7A492AC}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
@@ -716,702 +682,534 @@
         <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>495</v>
-      </c>
-      <c r="D2">
-        <v>40</v>
-      </c>
-      <c r="E2">
-        <v>288.08999999999997</v>
-      </c>
-      <c r="F2">
-        <v>558.72</v>
-      </c>
-      <c r="G2">
-        <v>40</v>
-      </c>
-      <c r="H2">
-        <v>335.23200000000003</v>
+      <c r="A2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="5">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F2" s="5">
+        <v>8.25</v>
+      </c>
+      <c r="G2" s="5">
+        <v>40</v>
+      </c>
+      <c r="H2" s="5">
+        <v>4.95</v>
+      </c>
+      <c r="I2" s="5">
+        <v>4.4000000000000004</v>
       </c>
       <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>297.01</v>
-      </c>
-      <c r="D3">
-        <v>40</v>
-      </c>
-      <c r="E3">
-        <v>172.85982000000001</v>
-      </c>
-      <c r="F3">
-        <v>345.721</v>
-      </c>
-      <c r="G3">
-        <v>40</v>
-      </c>
-      <c r="H3">
-        <v>207.43260000000001</v>
+      <c r="A3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="6">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F3" s="6">
+        <v>8.25</v>
+      </c>
+      <c r="G3" s="6">
+        <v>40</v>
+      </c>
+      <c r="H3" s="6">
+        <v>4.95</v>
+      </c>
+      <c r="I3" s="6">
+        <v>4.5999999999999996</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>57</v>
+      </c>
+      <c r="K3">
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>224.4</v>
-      </c>
-      <c r="D4">
+      <c r="A4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D4" s="5">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>224.4</v>
-      </c>
-      <c r="F4">
-        <v>448.8</v>
-      </c>
-      <c r="G4">
-        <v>40</v>
-      </c>
-      <c r="H4">
-        <v>269.27999999999997</v>
+      <c r="E4" s="5">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F4" s="5">
+        <v>8.25</v>
+      </c>
+      <c r="G4" s="5">
+        <v>40</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4.95</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4.4000000000000004</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>58</v>
+      </c>
+      <c r="K4" s="5">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5">
-        <v>211</v>
-      </c>
-      <c r="D5">
-        <v>40</v>
-      </c>
-      <c r="E5">
-        <v>101.495853</v>
-      </c>
-      <c r="F5">
-        <v>211.5</v>
-      </c>
-      <c r="G5">
-        <v>40</v>
-      </c>
-      <c r="H5">
-        <v>126.9</v>
+      <c r="A5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="6">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>3.5424000000000002</v>
+      </c>
+      <c r="F5" s="6">
+        <v>8.25</v>
+      </c>
+      <c r="G5" s="6">
+        <v>40</v>
+      </c>
+      <c r="H5" s="6">
+        <v>4.95</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4.5999999999999996</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>58</v>
+      </c>
+      <c r="K5">
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C6">
-        <v>252</v>
+        <v>75.349999999999994</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>146.66399999999999</v>
+        <v>75.349999999999994</v>
       </c>
       <c r="F6">
-        <v>303</v>
+        <v>156.66999999999999</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
-        <v>181.8</v>
+        <v>94.001999999999995</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C7">
-        <v>130</v>
+        <v>67.319999999999993</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>126.1</v>
+        <v>67.319999999999993</v>
       </c>
       <c r="F7">
-        <v>252.2</v>
+        <v>134.63999999999999</v>
       </c>
       <c r="G7">
         <v>40</v>
       </c>
       <c r="H7">
-        <v>151.32</v>
+        <v>80.784000000000006</v>
       </c>
       <c r="I7">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s">
         <v>52</v>
       </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C8">
-        <v>23.92</v>
+        <v>91.01</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E8">
-        <v>14.7706</v>
+        <v>43.777903000000002</v>
       </c>
       <c r="F8">
-        <v>29.54</v>
+        <v>91.25</v>
       </c>
       <c r="G8">
         <v>40</v>
       </c>
       <c r="H8">
-        <v>17.724</v>
-      </c>
-      <c r="I8">
-        <v>14.77</v>
+        <v>54.75</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>15.26</v>
+        <v>297.01</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E9">
-        <v>9.4230499999999999</v>
+        <v>172.85982000000001</v>
       </c>
       <c r="F9">
-        <v>18.850000000000001</v>
+        <v>345.721</v>
       </c>
       <c r="G9">
         <v>40</v>
       </c>
       <c r="H9">
-        <v>11.31</v>
-      </c>
-      <c r="I9">
-        <v>9.43</v>
+        <v>207.43260000000001</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>17.899999000000001</v>
+        <v>495</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E10">
-        <v>17.899999000000001</v>
+        <v>288.08999999999997</v>
       </c>
       <c r="F10">
-        <v>41.67</v>
+        <v>558.72</v>
       </c>
       <c r="G10">
         <v>40</v>
       </c>
       <c r="H10">
-        <v>25.001999999999999</v>
-      </c>
-      <c r="I10">
-        <v>21.501719999999999</v>
+        <v>335.23200000000003</v>
       </c>
       <c r="J10" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C11">
-        <v>329</v>
+        <v>23.92</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E11">
-        <v>197.4</v>
+        <v>14.7706</v>
       </c>
       <c r="F11">
-        <v>399</v>
+        <v>29.54</v>
       </c>
       <c r="G11">
         <v>40</v>
       </c>
       <c r="H11">
-        <v>239.4</v>
+        <v>17.724</v>
+      </c>
+      <c r="I11">
+        <v>14.77</v>
       </c>
       <c r="J11" t="s">
-        <v>56</v>
+        <v>45</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>15.26</v>
+      </c>
+      <c r="D12">
         <v>35</v>
       </c>
-      <c r="C12">
-        <v>75.349999999999994</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
       <c r="E12">
-        <v>75.349999999999994</v>
+        <v>9.4230499999999999</v>
       </c>
       <c r="F12">
-        <v>156.66999999999999</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="G12">
         <v>40</v>
       </c>
       <c r="H12">
-        <v>94.001999999999995</v>
+        <v>11.31</v>
+      </c>
+      <c r="I12">
+        <v>9.43</v>
       </c>
       <c r="J12" t="s">
-        <v>57</v>
+        <v>46</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>39.200000000000003</v>
+        <v>224.4</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>39.200000000000003</v>
+        <v>224.4</v>
       </c>
       <c r="F13">
-        <v>78.400000000000006</v>
+        <v>448.8</v>
       </c>
       <c r="G13">
         <v>40</v>
       </c>
       <c r="H13">
-        <v>47.04</v>
+        <v>269.27999999999997</v>
       </c>
       <c r="J13" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
       <c r="C14">
-        <v>348</v>
+        <v>44.225999999999999</v>
       </c>
       <c r="D14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>167.396004</v>
+        <v>44.225999999999999</v>
       </c>
       <c r="F14">
-        <v>348.75</v>
+        <v>92.14</v>
       </c>
       <c r="G14">
         <v>40</v>
       </c>
       <c r="H14">
-        <v>209.25</v>
+        <v>55.283999999999999</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15">
+      <c r="A15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="3">
+        <v>130</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3">
+        <v>126.1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>252.2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>40</v>
+      </c>
+      <c r="H15" s="3">
+        <v>151.32</v>
+      </c>
+      <c r="I15" s="4">
+        <v>145</v>
+      </c>
+      <c r="J15" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="3">
         <v>66.42</v>
       </c>
-      <c r="D15">
+      <c r="D16" s="3">
         <v>0</v>
       </c>
-      <c r="E15">
+      <c r="E16" s="3">
         <v>66.42</v>
       </c>
-      <c r="F15">
+      <c r="F16" s="3">
         <v>133</v>
       </c>
-      <c r="G15">
-        <v>40</v>
-      </c>
-      <c r="H15">
+      <c r="G16" s="3">
+        <v>40</v>
+      </c>
+      <c r="H16" s="3">
         <v>79.8</v>
       </c>
-      <c r="J15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16">
-        <v>44.225999999999999</v>
-      </c>
-      <c r="D16">
+      <c r="I16" s="4"/>
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="D17" s="3">
         <v>0</v>
       </c>
-      <c r="E16">
-        <v>44.225999999999999</v>
-      </c>
-      <c r="F16">
-        <v>92.14</v>
-      </c>
-      <c r="G16">
-        <v>40</v>
-      </c>
-      <c r="H16">
-        <v>55.283999999999999</v>
-      </c>
-      <c r="J16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17">
-        <v>42.15</v>
-      </c>
-      <c r="D17">
-        <v>40</v>
-      </c>
-      <c r="E17">
-        <v>22.255199999999999</v>
-      </c>
-      <c r="F17">
-        <v>48.2</v>
-      </c>
-      <c r="G17">
-        <v>40</v>
-      </c>
-      <c r="H17">
-        <v>28.92</v>
-      </c>
+      <c r="E17" s="3">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="F17" s="3">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G17" s="3">
+        <v>40</v>
+      </c>
+      <c r="H17" s="3">
+        <v>47.04</v>
+      </c>
+      <c r="I17" s="4"/>
       <c r="J17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18">
-        <v>91.01</v>
-      </c>
-      <c r="D18">
-        <v>40</v>
-      </c>
-      <c r="E18">
-        <v>43.777903000000002</v>
-      </c>
-      <c r="F18">
-        <v>91.25</v>
-      </c>
-      <c r="G18">
-        <v>40</v>
-      </c>
-      <c r="H18">
-        <v>54.75</v>
-      </c>
-      <c r="J18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19">
-        <v>67.319999999999993</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>67.319999999999993</v>
-      </c>
-      <c r="F19">
-        <v>134.63999999999999</v>
-      </c>
-      <c r="G19">
-        <v>40</v>
-      </c>
-      <c r="H19">
-        <v>80.784000000000006</v>
-      </c>
-      <c r="I19">
-        <v>76</v>
-      </c>
-      <c r="J19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8.25</v>
-      </c>
-      <c r="G20" s="2">
-        <v>40</v>
-      </c>
-      <c r="H20" s="2">
-        <v>4.95</v>
-      </c>
-      <c r="I20" s="5">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J20" t="s">
-        <v>69</v>
-      </c>
-      <c r="K20" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="F21" s="4">
-        <v>8.25</v>
-      </c>
-      <c r="G21" s="4">
-        <v>40</v>
-      </c>
-      <c r="H21" s="4">
-        <v>4.95</v>
-      </c>
-      <c r="I21" s="6">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J21" t="s">
-        <v>69</v>
-      </c>
-      <c r="K21">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8.25</v>
-      </c>
-      <c r="G22" s="2">
-        <v>40</v>
-      </c>
-      <c r="H22" s="2">
-        <v>4.95</v>
-      </c>
-      <c r="I22" s="5">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J22" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>3.5424000000000002</v>
-      </c>
-      <c r="F23" s="4">
-        <v>8.25</v>
-      </c>
-      <c r="G23" s="4">
-        <v>40</v>
-      </c>
-      <c r="H23" s="4">
-        <v>4.95</v>
-      </c>
-      <c r="I23" s="6">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J23" t="s">
-        <v>70</v>
-      </c>
-      <c r="K23">
-        <v>120</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I20:I23 K20 K22">
+  <autoFilter ref="A1:K17" xr:uid="{0ED20D23-1B19-4647-8C7A-B348F7A492AC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
+      <sortCondition ref="A1:A17"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="K16 I16:I17">
     <cfRule type="expression" priority="1">
-      <formula>AND(ISNUMBER(I24), I24&gt;0, TRIM(I24)&lt;&gt;"")</formula>
+      <formula>AND(ISNUMBER(I20), I20&gt;0, TRIM(I20)&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15 K15">
+    <cfRule type="expression" priority="2">
+      <formula>AND(ISNUMBER(I18), I18&gt;0, TRIM(I18)&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1474,7 +1272,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -1486,7 +1284,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1498,7 +1296,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1510,7 +1308,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1522,7 +1320,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1534,7 +1332,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -1546,7 +1344,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1558,7 +1356,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1570,7 +1368,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -1582,7 +1380,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -1594,7 +1392,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -1606,7 +1404,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -1618,7 +1416,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -1630,7 +1428,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -1642,7 +1440,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -1654,7 +1452,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
